--- a/artfynd/A 63810-2021 artfynd.xlsx
+++ b/artfynd/A 63810-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63810-2021 artfynd.xlsx
+++ b/artfynd/A 63810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95771615</v>
+        <v>95771438</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476201.2771679835</v>
+        <v>476099</v>
       </c>
       <c r="R2" t="n">
-        <v>6786380.268043645</v>
+        <v>6786442</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -751,24 +746,9 @@
           <t>2021-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>flera länge bålar</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95771550</v>
+        <v>95771582</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -839,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476183.0288668581</v>
+        <v>476186</v>
       </c>
       <c r="R3" t="n">
-        <v>6786393.884772745</v>
+        <v>6786382</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,19 +847,14 @@
           <t>2021-08-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-28</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>flera träd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95771634</v>
+        <v>95771606</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476202.9443671181</v>
+        <v>476201</v>
       </c>
       <c r="R4" t="n">
-        <v>6786483.862660996</v>
+        <v>6786380</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -988,19 +953,9 @@
           <t>2021-08-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,15 +983,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95771571</v>
+        <v>95783512</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1044,21 +994,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476186.3255595903</v>
+        <v>476276</v>
       </c>
       <c r="R5" t="n">
-        <v>6786381.815068278</v>
+        <v>6786530</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1101,22 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1144,15 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95771582</v>
+        <v>95783587</v>
       </c>
       <c r="B6" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,10 +1122,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476186.3255595903</v>
+        <v>476302</v>
       </c>
       <c r="R6" t="n">
-        <v>6786381.815068278</v>
+        <v>6786538</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1217,27 +1152,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>flera träd</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1265,15 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95771606</v>
+        <v>95783609</v>
       </c>
       <c r="B7" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,10 +1223,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476201.2771679835</v>
+        <v>476333</v>
       </c>
       <c r="R7" t="n">
-        <v>6786380.268043645</v>
+        <v>6786563</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1338,22 +1253,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2021-08-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,19 +1286,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95783519</v>
+        <v>95771440</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1424,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476276.1344834787</v>
+        <v>476099</v>
       </c>
       <c r="R8" t="n">
-        <v>6786530.10965097</v>
+        <v>6786442</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1454,22 +1354,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,37 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95783512</v>
+        <v>95771550</v>
       </c>
       <c r="B9" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1540,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476276.1344834787</v>
+        <v>476183</v>
       </c>
       <c r="R9" t="n">
-        <v>6786530.10965097</v>
+        <v>6786394</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1570,22 +1455,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,19 +1488,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>95783529</v>
+        <v>95771571</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1656,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476265.42598677</v>
+        <v>476186</v>
       </c>
       <c r="R10" t="n">
-        <v>6786516.689491331</v>
+        <v>6786382</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1686,22 +1556,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,37 +1589,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>95783587</v>
+        <v>95771615</v>
       </c>
       <c r="B11" t="n">
-        <v>77541</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1627,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476302.2504524845</v>
+        <v>476201</v>
       </c>
       <c r="R11" t="n">
-        <v>6786538.125195236</v>
+        <v>6786380</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1802,22 +1657,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>flera länge bålar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,6 +1692,612 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95771634</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Råtjärnen Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>476203</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6786484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-28</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95783519</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Råtjärnen Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>476276</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6786530</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95783529</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Råtjärnen Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>476266</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6786517</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>95783570</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Råtjärnen Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>476263</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6786535</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>95783614</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Råtjärnen Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>476333</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6786563</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111227664</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Grönklitt, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>476729</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6786567</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63810-2021 artfynd.xlsx
+++ b/artfynd/A 63810-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771582</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771606</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771550</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1081,6 +1101,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771571</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771615</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771438</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1389,6 +1424,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783512</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783587</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1591,6 +1636,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783609</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1692,6 +1742,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771440</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1793,6 +1848,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95771634</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1894,6 +1954,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783519</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783529</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2096,6 +2166,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783570</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2197,6 +2272,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95783614</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,8 +2378,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111227664</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>